--- a/event_registration_forms/009_population_health_data_science_workshop_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/009_population_health_data_science_workshop_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email_confirmed</t>
+          <t>email_confirmed_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>note_confirmed</t>
+          <t>note_confirmed_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>First Name 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>last_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Last Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>email_confirmed_choices</t>
+          <t>email_confirmed_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>email_confirmed_choices</t>
+          <t>email_confirmed_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>email_confirmed_choices</t>
+          <t>email_confirmed_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1640,7 +1640,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>note_confirmed_choices</t>
+          <t>note_confirmed_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>note_confirmed_choices</t>
+          <t>note_confirmed_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1674,7 +1674,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>note_confirmed_choices</t>
+          <t>note_confirmed_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
